--- a/tests.xlsx
+++ b/tests.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\privat\gimbal_test_01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\privat\gimbal_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F95F316-423B-46F2-8A7A-C82F8BD3DAF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B29EE48-7519-4FEE-978F-33A84D5FCDDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8325" yWindow="1185" windowWidth="27135" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1665" yWindow="1185" windowWidth="27135" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -477,7 +477,7 @@
         <v>7</v>
       </c>
       <c r="F17" s="1">
-        <v>12</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
@@ -492,7 +492,7 @@
       </c>
       <c r="F18" s="1">
         <f>F17*C18/(C17+C18)</f>
-        <v>3.1864406779661021</v>
+        <v>2.9474576271186441</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
